--- a/data/trans_orig/P36B01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B01-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de café o té en 2016</t>
+          <t>Población según la frecuencia de consumo de café o té en 2016 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>105637</t>
+          <t>102870</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145214</t>
+          <t>144526</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118595</t>
+          <t>119709</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>166886</t>
+          <t>165167</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>231708</t>
+          <t>233526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>294067</t>
+          <t>292587</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>12199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29290</t>
+          <t>29122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>18537</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>20385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42609</t>
+          <t>42205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16578</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25489</t>
+          <t>26063</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20397</t>
+          <t>22224</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32576</t>
+          <t>30978</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>571989</t>
+          <t>573230</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>615940</t>
+          <t>617021</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>794122</t>
+          <t>795325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>845124</t>
+          <t>844037</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1380940</t>
+          <t>1382925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1449274</t>
+          <t>1450248</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,03%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>250103</t>
+          <t>253021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>314952</t>
+          <t>317403</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>236589</t>
+          <t>234598</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>293876</t>
+          <t>294046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>508769</t>
+          <t>502504</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>594685</t>
+          <t>590736</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31769</t>
+          <t>29987</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>55976</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39908</t>
+          <t>41221</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55627</t>
+          <t>56438</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90512</t>
+          <t>89231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39159</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67666</t>
+          <t>68491</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19360</t>
+          <t>19432</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39629</t>
+          <t>39829</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64625</t>
+          <t>63336</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>100261</t>
+          <t>100633</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49345</t>
+          <t>47734</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81437</t>
+          <t>81380</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29929</t>
+          <t>30554</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56006</t>
+          <t>56617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86463</t>
+          <t>85018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127786</t>
+          <t>126087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1595719</t>
+          <t>1598212</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1672238</t>
+          <t>1672080</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1586929</t>
+          <t>1584659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1654245</t>
+          <t>1653896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3199560</t>
+          <t>3203708</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3301417</t>
+          <t>3304598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49123</t>
+          <t>50230</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80689</t>
+          <t>81717</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65933</t>
+          <t>66230</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>95892</t>
+          <t>95552</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139735</t>
+          <t>139759</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>954</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18145</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17434</t>
+          <t>18274</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11387</t>
+          <t>11682</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27254</t>
+          <t>28495</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19713</t>
+          <t>18755</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41847</t>
+          <t>38843</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16484</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26343</t>
+          <t>27332</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17227</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37033</t>
+          <t>37180</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>439334</t>
+          <t>439555</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>475386</t>
+          <t>474630</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>434501</t>
+          <t>434505</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>468770</t>
+          <t>468976</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>881195</t>
+          <t>882478</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>932791</t>
+          <t>935046</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,76%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>430522</t>
+          <t>436104</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>511225</t>
+          <t>518793</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>413925</t>
+          <t>417099</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>494408</t>
+          <t>499365</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>867990</t>
+          <t>867185</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>979720</t>
+          <t>977444</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50244</t>
+          <t>49744</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>81699</t>
+          <t>81422</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>35413</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63360</t>
+          <t>61854</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94398</t>
+          <t>94084</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>136120</t>
+          <t>135636</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53906</t>
+          <t>55457</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>88663</t>
+          <t>89792</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40913</t>
+          <t>40954</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>69316</t>
+          <t>68411</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>101957</t>
+          <t>103748</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>147969</t>
+          <t>149030</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65125</t>
+          <t>65527</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102388</t>
+          <t>100604</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55932</t>
+          <t>54879</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90064</t>
+          <t>87995</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>125875</t>
+          <t>129897</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>176594</t>
+          <t>178314</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2639846</t>
+          <t>2634464</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2736537</t>
+          <t>2730782</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2848200</t>
+          <t>2844706</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2938850</t>
+          <t>2938656</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5522270</t>
+          <t>5516363</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5651675</t>
+          <t>5646849</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,89%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B01-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>102870</t>
+          <t>103979</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>144526</t>
+          <t>143501</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119709</t>
+          <t>118800</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>165167</t>
+          <t>166109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>233526</t>
+          <t>232584</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>292587</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12199</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29122</t>
+          <t>28079</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20385</t>
+          <t>20695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42205</t>
+          <t>43771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>15766</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>15239</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>9074</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26063</t>
+          <t>26193</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>15695</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22224</t>
+          <t>22389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12633</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>31154</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>573230</t>
+          <t>571224</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>617021</t>
+          <t>615493</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>795325</t>
+          <t>793197</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>844037</t>
+          <t>843965</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1382925</t>
+          <t>1380260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1450248</t>
+          <t>1449092</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>253021</t>
+          <t>253852</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>317403</t>
+          <t>316566</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>234598</t>
+          <t>235813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>294046</t>
+          <t>295679</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>502504</t>
+          <t>504618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>590736</t>
+          <t>594656</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29987</t>
+          <t>30460</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55976</t>
+          <t>57278</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,47 +1540,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>28467</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>18797</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>28467</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>19363</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>41221</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56438</t>
+          <t>55684</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89231</t>
+          <t>88843</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>40451</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68491</t>
+          <t>70282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19432</t>
+          <t>18301</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39829</t>
+          <t>40030</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63336</t>
+          <t>63813</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>100633</t>
+          <t>100859</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47734</t>
+          <t>49524</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81380</t>
+          <t>81967</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30554</t>
+          <t>30583</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56617</t>
+          <t>56824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85018</t>
+          <t>85896</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126087</t>
+          <t>129013</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1598212</t>
+          <t>1596134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1672080</t>
+          <t>1670027</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1584659</t>
+          <t>1588359</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1653896</t>
+          <t>1656415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3203708</t>
+          <t>3197318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3304598</t>
+          <t>3304539</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50230</t>
+          <t>49702</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81717</t>
+          <t>79478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37640</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66230</t>
+          <t>65317</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>95552</t>
+          <t>94326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139759</t>
+          <t>135709</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>964</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>14562</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18838</t>
+          <t>18434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18274</t>
+          <t>17826</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11682</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28495</t>
+          <t>27492</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18755</t>
+          <t>19754</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38843</t>
+          <t>41123</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16658</t>
+          <t>16804</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9360</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27332</t>
+          <t>26661</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37180</t>
+          <t>37526</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>439555</t>
+          <t>438244</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>474630</t>
+          <t>473200</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>434505</t>
+          <t>434696</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>468976</t>
+          <t>469079</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>882478</t>
+          <t>885504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>935046</t>
+          <t>934989</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>436104</t>
+          <t>432505</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>518793</t>
+          <t>510013</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>417099</t>
+          <t>416024</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>499365</t>
+          <t>498363</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>867185</t>
+          <t>867690</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>977444</t>
+          <t>978902</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>49744</t>
+          <t>51463</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>81422</t>
+          <t>81895</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35413</t>
+          <t>34654</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>61854</t>
+          <t>61362</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94084</t>
+          <t>92525</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>135636</t>
+          <t>133073</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55457</t>
+          <t>53990</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>89792</t>
+          <t>90355</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40954</t>
+          <t>40632</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>68411</t>
+          <t>70130</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>103748</t>
+          <t>103426</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>149030</t>
+          <t>147867</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65527</t>
+          <t>63788</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>100604</t>
+          <t>101215</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54879</t>
+          <t>55226</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87995</t>
+          <t>89607</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>129897</t>
+          <t>129164</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>178314</t>
+          <t>178475</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2634464</t>
+          <t>2637018</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2730782</t>
+          <t>2732924</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2844706</t>
+          <t>2846893</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2938656</t>
+          <t>2939531</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5516363</t>
+          <t>5522455</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5646849</t>
+          <t>5645233</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,87%</t>
         </is>
       </c>
     </row>
